--- a/Fischer_Tropsch/FischerTropsch_Naphta_Bio_Brownfield_Memmingen/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Naphta_Bio_Brownfield_Memmingen/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Bio_Brownfield_Leuna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Bio_Brownfield_Memmingen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35AEE0A-F31C-4187-BD6D-2015FC3587F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787619BA-4D9A-4139-96D5-01FAE47C5BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1392,10 +1392,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1555,114 +1555,101 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1993,46 +1980,46 @@
   <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="14" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="14" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="14"/>
+    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="24" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="28"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="50" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2049,338 +2036,338 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="48"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E3" s="2">
         <v>50</v>
       </c>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="1" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="48"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="41"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="16">
-        <v>1000</v>
-      </c>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="14">
+        <v>1500</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="48"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="41"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="3">
         <v>0.03</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="48"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="41"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="4">
         <v>20</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="48"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="41"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="3">
         <v>0.08</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="48"/>
-      <c r="B8" s="59" t="s">
+      <c r="A8" s="41"/>
+      <c r="B8" s="51" t="s">
         <v>303</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="16">
         <v>38.99</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="15" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="48"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="41"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="2">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="1" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="48"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="41"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="2">
         <v>2440</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="2" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="48"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="14" t="s">
+      <c r="A11" s="41"/>
+      <c r="B11" s="48"/>
+      <c r="C11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="3">
         <v>0.03</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="14" t="s">
+      <c r="A12" s="41"/>
+      <c r="B12" s="48"/>
+      <c r="C12" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="E12" s="15">
+      <c r="E12" s="2">
         <v>0.63</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="1" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="41"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="2">
         <v>4.8600000000000003</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="1" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="14" t="s">
+      <c r="A14" s="41"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="2">
         <v>0.39</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="1" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="41"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="4">
         <v>20</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="48"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="21" t="s">
+      <c r="A16" s="41"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="18">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="48"/>
-      <c r="B17" s="59" t="s">
+      <c r="A17" s="41"/>
+      <c r="B17" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="E17" s="23">
+      <c r="E17" s="19">
         <v>3.7</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="14" t="s">
+      <c r="A18" s="41"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="3">
         <v>0.27</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="1" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="48"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="14" t="s">
+      <c r="A19" s="41"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="3">
         <v>700</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="1" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="48"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="14" t="s">
+      <c r="A20" s="41"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="3">
         <v>0.02</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="48"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="41"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="3">
         <v>20</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="48"/>
-      <c r="B22" s="60"/>
-      <c r="C22" s="21" t="s">
+      <c r="A22" s="41"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="17" t="s">
         <v>244</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="18">
         <v>0.05</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
-      <c r="B23" s="46" t="s">
+      <c r="A23" s="41"/>
+      <c r="B23" s="39" t="s">
         <v>386</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="D23" s="35" t="s">
         <v>387</v>
       </c>
       <c r="E23" s="11">
@@ -2391,12 +2378,12 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
-      <c r="B24" s="46"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="39"/>
       <c r="C24" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D24" s="42" t="s">
+      <c r="D24" s="35" t="s">
         <v>388</v>
       </c>
       <c r="E24" s="11">
@@ -2407,12 +2394,12 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="48"/>
-      <c r="B25" s="46"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="39"/>
       <c r="C25" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="42" t="s">
+      <c r="D25" s="35" t="s">
         <v>389</v>
       </c>
       <c r="E25" s="11">
@@ -2423,12 +2410,12 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
-      <c r="B26" s="46"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="39"/>
       <c r="C26" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="D26" s="42" t="s">
+      <c r="D26" s="35" t="s">
         <v>391</v>
       </c>
       <c r="E26" s="10">
@@ -2439,24 +2426,24 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="48"/>
-      <c r="B27" s="46"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="39"/>
       <c r="C27" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="35" t="s">
         <v>392</v>
       </c>
       <c r="E27" s="10">
         <v>2.5</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="35" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="48"/>
-      <c r="B28" s="46"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="39"/>
       <c r="C28" s="1" t="s">
         <v>394</v>
       </c>
@@ -2471,8 +2458,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="48"/>
-      <c r="B29" s="46"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="39"/>
       <c r="C29" s="1" t="s">
         <v>397</v>
       </c>
@@ -2487,12 +2474,12 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="48"/>
-      <c r="B30" s="46"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="39"/>
       <c r="C30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D30" s="42" t="s">
+      <c r="D30" s="35" t="s">
         <v>400</v>
       </c>
       <c r="E30" s="9">
@@ -2503,12 +2490,12 @@
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="48"/>
-      <c r="B31" s="46"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="39"/>
       <c r="C31" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D31" s="42" t="s">
+      <c r="D31" s="35" t="s">
         <v>401</v>
       </c>
       <c r="E31" s="10">
@@ -2519,10 +2506,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="47" t="s">
+      <c r="A32" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="51" t="s">
+      <c r="B32" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C32" s="12" t="s">
@@ -2531,7 +2518,7 @@
       <c r="D32" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="25">
         <v>490</v>
       </c>
       <c r="F32" s="12" t="s">
@@ -2539,120 +2526,120 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="48"/>
-      <c r="B33" s="52"/>
-      <c r="C33" s="14" t="s">
+      <c r="A33" s="41"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="3">
         <v>0.01</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="48"/>
-      <c r="B34" s="52"/>
-      <c r="C34" s="14" t="s">
+      <c r="A34" s="41"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="4">
         <v>20</v>
       </c>
-      <c r="F34" s="14" t="s">
+      <c r="F34" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="48"/>
-      <c r="B35" s="52"/>
-      <c r="C35" s="14" t="s">
+      <c r="A35" s="41"/>
+      <c r="B35" s="44"/>
+      <c r="C35" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="26">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F35" s="14" t="s">
+      <c r="F35" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="41"/>
+      <c r="B36" s="44"/>
+      <c r="C36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="3">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F36" s="14" t="s">
+      <c r="F36" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
-      <c r="B37" s="52"/>
-      <c r="C37" s="14" t="s">
+      <c r="A37" s="41"/>
+      <c r="B37" s="44"/>
+      <c r="C37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="D37" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="3">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F37" s="14" t="s">
+      <c r="F37" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="14" t="s">
+      <c r="A38" s="41"/>
+      <c r="B38" s="44"/>
+      <c r="C38" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="D38" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="3">
         <v>0.05</v>
       </c>
-      <c r="F38" s="14" t="s">
+      <c r="F38" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="48"/>
-      <c r="B39" s="53"/>
-      <c r="C39" s="21" t="s">
+      <c r="A39" s="41"/>
+      <c r="B39" s="45"/>
+      <c r="C39" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="D39" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="18">
         <v>0</v>
       </c>
-      <c r="F39" s="21" t="s">
+      <c r="F39" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
-      <c r="B40" s="54" t="s">
+      <c r="A40" s="41"/>
+      <c r="B40" s="46" t="s">
         <v>278</v>
       </c>
       <c r="C40" s="12" t="s">
@@ -2661,7 +2648,7 @@
       <c r="D40" s="12" t="s">
         <v>279</v>
       </c>
-      <c r="E40" s="29">
+      <c r="E40" s="25">
         <v>2.83</v>
       </c>
       <c r="F40" s="12" t="s">
@@ -2669,636 +2656,636 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
-      <c r="B41" s="52"/>
-      <c r="C41" s="14" t="s">
+      <c r="A41" s="41"/>
+      <c r="B41" s="44"/>
+      <c r="C41" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="3">
         <v>0.03</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
-      <c r="B42" s="52"/>
-      <c r="C42" s="14" t="s">
+      <c r="A42" s="41"/>
+      <c r="B42" s="44"/>
+      <c r="C42" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="4">
         <v>30</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
-      <c r="B43" s="52"/>
-      <c r="C43" s="14" t="s">
+      <c r="A43" s="41"/>
+      <c r="B43" s="44"/>
+      <c r="C43" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="D43" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="3">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F43" s="14" t="s">
+      <c r="F43" s="1" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
-      <c r="B44" s="52"/>
-      <c r="C44" s="14" t="s">
+      <c r="A44" s="41"/>
+      <c r="B44" s="44"/>
+      <c r="C44" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="14" t="s">
+      <c r="D44" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="3">
         <v>0.98</v>
       </c>
-      <c r="F44" s="14" t="s">
+      <c r="F44" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="14" t="s">
+      <c r="A45" s="41"/>
+      <c r="B45" s="44"/>
+      <c r="C45" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="14" t="s">
+      <c r="D45" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="3">
         <v>0.98</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="48"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="14" t="s">
+      <c r="A46" s="41"/>
+      <c r="B46" s="44"/>
+      <c r="C46" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D46" s="14" t="s">
+      <c r="D46" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="3">
         <v>0.05</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="48"/>
-      <c r="B47" s="52"/>
-      <c r="C47" s="21" t="s">
+      <c r="A47" s="41"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="18">
         <v>0</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
-      <c r="B48" s="54" t="s">
+      <c r="A48" s="41"/>
+      <c r="B48" s="46" t="s">
         <v>201</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="19">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F48" s="15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="48"/>
-      <c r="B49" s="56"/>
-      <c r="C49" s="14" t="s">
+      <c r="A49" s="41"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E49" s="15">
+      <c r="E49" s="2">
         <f>E50*4</f>
         <v>424</v>
       </c>
-      <c r="F49" s="14" t="s">
+      <c r="F49" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="48"/>
-      <c r="B50" s="56"/>
-      <c r="C50" s="14" t="s">
+      <c r="A50" s="41"/>
+      <c r="B50" s="48"/>
+      <c r="C50" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="2">
         <v>106</v>
       </c>
-      <c r="F50" s="14" t="s">
+      <c r="F50" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="48"/>
-      <c r="B51" s="56"/>
-      <c r="C51" s="14" t="s">
+      <c r="A51" s="41"/>
+      <c r="B51" s="48"/>
+      <c r="C51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E51" s="17">
+      <c r="E51" s="3">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F51" s="14" t="s">
+      <c r="F51" s="1" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="48"/>
-      <c r="B52" s="56"/>
-      <c r="C52" s="14" t="s">
+      <c r="A52" s="41"/>
+      <c r="B52" s="48"/>
+      <c r="C52" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E52" s="17">
+      <c r="E52" s="3">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F52" s="14" t="s">
+      <c r="F52" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="48"/>
-      <c r="B53" s="56"/>
-      <c r="C53" s="14" t="s">
+      <c r="A53" s="41"/>
+      <c r="B53" s="48"/>
+      <c r="C53" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E53" s="17">
+      <c r="E53" s="3">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F53" s="14" t="s">
+      <c r="F53" s="1" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="48"/>
-      <c r="B54" s="56"/>
-      <c r="C54" s="14" t="s">
+      <c r="A54" s="41"/>
+      <c r="B54" s="48"/>
+      <c r="C54" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E54" s="15">
+      <c r="E54" s="2">
         <v>0.25</v>
       </c>
-      <c r="F54" s="14" t="s">
+      <c r="F54" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="48"/>
-      <c r="B55" s="56"/>
-      <c r="C55" s="14" t="s">
+      <c r="A55" s="41"/>
+      <c r="B55" s="48"/>
+      <c r="C55" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E55" s="17">
+      <c r="E55" s="3">
         <v>0</v>
       </c>
-      <c r="F55" s="14" t="s">
+      <c r="F55" s="1" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="48"/>
-      <c r="B56" s="56"/>
-      <c r="C56" s="14" t="s">
+      <c r="A56" s="41"/>
+      <c r="B56" s="48"/>
+      <c r="C56" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D56" s="14" t="s">
+      <c r="D56" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="4">
         <v>15</v>
       </c>
-      <c r="F56" s="14" t="s">
+      <c r="F56" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="49"/>
-      <c r="B57" s="57"/>
-      <c r="C57" s="31" t="s">
+      <c r="A57" s="42"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="28">
         <v>0.1</v>
       </c>
-      <c r="F57" s="31" t="s">
+      <c r="F57" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="47" t="s">
+      <c r="A58" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B58" s="44" t="s">
+      <c r="B58" s="37" t="s">
         <v>73</v>
       </c>
-      <c r="C58" s="35" t="s">
+      <c r="C58" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="D58" s="35" t="s">
+      <c r="D58" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="E58" s="36">
+      <c r="E58" s="32">
         <v>0.1699</v>
       </c>
-      <c r="F58" s="35" t="s">
+      <c r="F58" s="31" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="50"/>
-      <c r="B59" s="43" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="41"/>
+      <c r="B59" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="C59" s="42" t="s">
+      <c r="C59" s="35" t="s">
         <v>402</v>
       </c>
-      <c r="D59" s="42" t="s">
+      <c r="D59" s="35" t="s">
         <v>403</v>
       </c>
       <c r="E59" s="10">
         <v>0</v>
       </c>
-      <c r="F59" s="42" t="s">
+      <c r="F59" s="35" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="48"/>
-      <c r="B60" s="54" t="s">
+      <c r="A60" s="41"/>
+      <c r="B60" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D60" s="19" t="s">
+      <c r="D60" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="19">
         <v>0.99</v>
       </c>
-      <c r="F60" s="19" t="s">
+      <c r="F60" s="15" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="48"/>
-      <c r="B61" s="52"/>
-      <c r="C61" s="14" t="s">
+      <c r="A61" s="41"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E61" s="5">
         <v>1100</v>
       </c>
-      <c r="F61" s="14" t="s">
+      <c r="F61" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="48"/>
-      <c r="B62" s="52"/>
-      <c r="C62" s="14" t="s">
+      <c r="A62" s="41"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="1" t="s">
         <v>44</v>
       </c>
       <c r="E62" s="5">
         <v>17.84</v>
       </c>
-      <c r="F62" s="14" t="s">
+      <c r="F62" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="48"/>
-      <c r="B63" s="52"/>
-      <c r="C63" s="14" t="s">
+      <c r="A63" s="41"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E63" s="15">
+      <c r="E63" s="2">
         <v>0</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F63" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="48"/>
-      <c r="B64" s="52"/>
-      <c r="C64" s="14" t="s">
+      <c r="A64" s="41"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E64" s="18">
+      <c r="E64" s="4">
         <v>25</v>
       </c>
-      <c r="F64" s="14" t="s">
+      <c r="F64" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="48"/>
-      <c r="B65" s="52"/>
-      <c r="C65" s="14" t="s">
+      <c r="A65" s="41"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="E65" s="15">
+      <c r="E65" s="2">
         <v>1000000</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="F65" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="48"/>
-      <c r="B66" s="53"/>
-      <c r="C66" s="21" t="s">
+      <c r="A66" s="41"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="21" t="s">
+      <c r="D66" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="E66" s="22">
+      <c r="E66" s="18">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F66" s="21" t="s">
+      <c r="F66" s="17" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="48"/>
-      <c r="B67" s="54" t="s">
+      <c r="A67" s="41"/>
+      <c r="B67" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D67" s="19" t="s">
+      <c r="D67" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E67" s="23">
+      <c r="E67" s="19">
         <v>0.997</v>
       </c>
-      <c r="F67" s="19" t="s">
+      <c r="F67" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="48"/>
-      <c r="B68" s="52"/>
-      <c r="C68" s="14" t="s">
+      <c r="A68" s="41"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="D68" s="1" t="s">
         <v>48</v>
       </c>
       <c r="E68" s="5">
         <v>1080</v>
       </c>
-      <c r="F68" s="14" t="s">
+      <c r="F68" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="48"/>
-      <c r="B69" s="52"/>
-      <c r="C69" s="14" t="s">
+      <c r="A69" s="41"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="1" t="s">
         <v>52</v>
       </c>
       <c r="E69" s="5">
         <v>12.68</v>
       </c>
-      <c r="F69" s="14" t="s">
+      <c r="F69" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="48"/>
-      <c r="B70" s="52"/>
-      <c r="C70" s="14" t="s">
+      <c r="A70" s="41"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E70" s="6">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F70" s="14" t="s">
+      <c r="F70" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="48"/>
-      <c r="B71" s="52"/>
-      <c r="C71" s="14" t="s">
+      <c r="A71" s="41"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E71" s="18">
+      <c r="E71" s="4">
         <v>25</v>
       </c>
-      <c r="F71" s="14" t="s">
+      <c r="F71" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="48"/>
-      <c r="B72" s="52"/>
-      <c r="C72" s="14" t="s">
+      <c r="A72" s="41"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E72" s="33">
+      <c r="E72" s="29">
         <v>1000000</v>
       </c>
-      <c r="F72" s="14" t="s">
+      <c r="F72" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="49"/>
-      <c r="B73" s="55"/>
-      <c r="C73" s="31" t="s">
+      <c r="A73" s="42"/>
+      <c r="B73" s="47"/>
+      <c r="C73" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="D73" s="31" t="s">
+      <c r="D73" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="E73" s="32">
+      <c r="E73" s="28">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F73" s="31" t="s">
+      <c r="F73" s="27" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="47" t="s">
+      <c r="A74" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="34" t="s">
+      <c r="B74" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="35" t="s">
+      <c r="C74" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="D74" s="35" t="s">
+      <c r="D74" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="E74" s="36">
+      <c r="E74" s="32">
         <v>-1E-4</v>
       </c>
-      <c r="F74" s="35" t="s">
+      <c r="F74" s="31" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="48"/>
-      <c r="B75" s="28" t="s">
+      <c r="A75" s="41"/>
+      <c r="B75" s="24" t="s">
         <v>261</v>
       </c>
-      <c r="C75" s="14" t="s">
+      <c r="C75" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="E75" s="17">
+      <c r="E75" s="3">
         <v>-1E-4</v>
       </c>
-      <c r="F75" s="14" t="s">
+      <c r="F75" s="1" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="48"/>
-      <c r="B76" s="37" t="s">
+      <c r="A76" s="41"/>
+      <c r="B76" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="C76" s="24" t="s">
+      <c r="C76" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="D76" s="24" t="s">
+      <c r="D76" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="E76" s="38">
+      <c r="E76" s="34">
         <v>-1.5</v>
       </c>
-      <c r="F76" s="24" t="s">
+      <c r="F76" s="20" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="48"/>
-      <c r="B77" s="37" t="s">
+      <c r="A77" s="41"/>
+      <c r="B77" s="33" t="s">
         <v>344</v>
       </c>
-      <c r="C77" s="24" t="s">
+      <c r="C77" s="20" t="s">
         <v>345</v>
       </c>
-      <c r="D77" s="24" t="s">
+      <c r="D77" s="20" t="s">
         <v>346</v>
       </c>
-      <c r="E77" s="38">
+      <c r="E77" s="34">
         <v>-0.55000000000000004</v>
       </c>
-      <c r="F77" s="24" t="s">
+      <c r="F77" s="20" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="49"/>
-      <c r="B78" s="26" t="s">
+      <c r="A78" s="42"/>
+      <c r="B78" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="C78" s="31" t="s">
+      <c r="C78" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="D78" s="31" t="s">
+      <c r="D78" s="27" t="s">
         <v>319</v>
       </c>
-      <c r="E78" s="32">
+      <c r="E78" s="28">
         <f>-2.2</f>
         <v>-2.2000000000000002</v>
       </c>
-      <c r="F78" s="31" t="s">
+      <c r="F78" s="27" t="s">
         <v>318</v>
       </c>
     </row>
@@ -3326,43 +3313,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F155"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="14" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="14" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="14" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="14" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="14"/>
+    <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.5546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="22" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="50" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -3377,425 +3364,425 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="48"/>
-      <c r="B3" s="56"/>
-      <c r="C3" s="14" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="14" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="48"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="14" t="s">
+      <c r="A4" s="41"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="16"/>
-      <c r="F4" s="14" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="48"/>
-      <c r="B5" s="56"/>
-      <c r="C5" s="14" t="s">
+      <c r="A5" s="41"/>
+      <c r="B5" s="48"/>
+      <c r="C5" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="E5" s="17"/>
-      <c r="F5" s="14" t="s">
+      <c r="E5" s="3"/>
+      <c r="F5" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="48"/>
-      <c r="B6" s="56"/>
-      <c r="C6" s="14" t="s">
+      <c r="A6" s="41"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="14" t="s">
+      <c r="D6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="14" t="s">
+      <c r="E6" s="4"/>
+      <c r="F6" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="48"/>
-      <c r="B7" s="56"/>
-      <c r="C7" s="14" t="s">
+      <c r="A7" s="41"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="14" t="s">
+      <c r="E7" s="4"/>
+      <c r="F7" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="48"/>
-      <c r="B8" s="56"/>
-      <c r="C8" s="14" t="s">
+      <c r="A8" s="41"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="14" t="s">
+      <c r="E8" s="4"/>
+      <c r="F8" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="48"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="14" t="s">
+      <c r="A9" s="41"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="14" t="s">
+      <c r="E9" s="4"/>
+      <c r="F9" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="48"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="14" t="s">
+      <c r="A10" s="41"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="14" t="s">
+      <c r="E10" s="4"/>
+      <c r="F10" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="48"/>
-      <c r="B11" s="56"/>
-      <c r="E11" s="17"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="48"/>
+      <c r="E11" s="3"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="48"/>
-      <c r="B12" s="59" t="s">
+      <c r="A12" s="41"/>
+      <c r="B12" s="51" t="s">
         <v>337</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="19" t="s">
+      <c r="E12" s="16"/>
+      <c r="F12" s="15" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="48"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="14" t="s">
+      <c r="A13" s="41"/>
+      <c r="B13" s="48"/>
+      <c r="C13" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="1" t="s">
         <v>330</v>
       </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="14" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="1" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="14" t="s">
+      <c r="A14" s="41"/>
+      <c r="B14" s="48"/>
+      <c r="C14" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="D14" s="14" t="s">
+      <c r="D14" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="14" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="1" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="14" t="s">
+      <c r="A15" s="41"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="D15" s="1" t="s">
         <v>320</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15" t="s">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="48"/>
-      <c r="B16" s="56"/>
-      <c r="C16" s="14" t="s">
+      <c r="A16" s="41"/>
+      <c r="B16" s="48"/>
+      <c r="C16" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="14" t="s">
+      <c r="E16" s="3"/>
+      <c r="F16" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="48"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="14" t="s">
+      <c r="A17" s="41"/>
+      <c r="B17" s="48"/>
+      <c r="C17" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="1" t="s">
         <v>322</v>
       </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="14" t="s">
+      <c r="E17" s="2"/>
+      <c r="F17" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="48"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="14" t="s">
+      <c r="A18" s="41"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="1" t="s">
         <v>323</v>
       </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="14" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="48"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="14" t="s">
+      <c r="A19" s="41"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="1" t="s">
         <v>324</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="14" t="s">
+      <c r="E19" s="4"/>
+      <c r="F19" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="48"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="14" t="s">
+      <c r="A20" s="41"/>
+      <c r="B20" s="48"/>
+      <c r="C20" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="14" t="s">
+      <c r="E20" s="4"/>
+      <c r="F20" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="48"/>
-      <c r="B21" s="56"/>
-      <c r="C21" s="14" t="s">
+      <c r="A21" s="41"/>
+      <c r="B21" s="48"/>
+      <c r="C21" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="14" t="s">
+      <c r="E21" s="4"/>
+      <c r="F21" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="48"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="14" t="s">
+      <c r="A22" s="41"/>
+      <c r="B22" s="48"/>
+      <c r="C22" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="14" t="s">
+      <c r="E22" s="4"/>
+      <c r="F22" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="48"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="21"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="17"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="17"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="48"/>
-      <c r="B24" s="59" t="s">
+      <c r="A24" s="41"/>
+      <c r="B24" s="51" t="s">
         <v>238</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="14" t="s">
+      <c r="E24" s="2"/>
+      <c r="F24" s="1" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="48"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="14" t="s">
+      <c r="A25" s="41"/>
+      <c r="B25" s="48"/>
+      <c r="C25" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="14" t="s">
+      <c r="E25" s="2"/>
+      <c r="F25" s="1" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="48"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="14" t="s">
+      <c r="A26" s="41"/>
+      <c r="B26" s="48"/>
+      <c r="C26" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="E26" s="17"/>
-      <c r="F26" s="14" t="s">
+      <c r="E26" s="3"/>
+      <c r="F26" s="1" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="48"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="14" t="s">
+      <c r="A27" s="41"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="D27" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="14" t="s">
+      <c r="E27" s="4"/>
+      <c r="F27" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="48"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="14" t="s">
+      <c r="A28" s="41"/>
+      <c r="B28" s="48"/>
+      <c r="C28" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="14" t="s">
+      <c r="E28" s="4"/>
+      <c r="F28" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="48"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="14" t="s">
+      <c r="A29" s="41"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="14" t="s">
+      <c r="E29" s="4"/>
+      <c r="F29" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="48"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="14" t="s">
+      <c r="A30" s="41"/>
+      <c r="B30" s="48"/>
+      <c r="C30" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="14" t="s">
+      <c r="E30" s="4"/>
+      <c r="F30" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="48"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="14" t="s">
+      <c r="A31" s="41"/>
+      <c r="B31" s="48"/>
+      <c r="C31" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="E31" s="17"/>
-      <c r="F31" s="14" t="s">
+      <c r="E31" s="3"/>
+      <c r="F31" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="48"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="14" t="s">
+      <c r="A32" s="41"/>
+      <c r="B32" s="48"/>
+      <c r="C32" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="E32" s="17"/>
-      <c r="F32" s="14" t="s">
+      <c r="E32" s="3"/>
+      <c r="F32" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="48"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="21"/>
+      <c r="A33" s="41"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="17"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="48"/>
-      <c r="B34" s="46" t="s">
+      <c r="A34" s="41"/>
+      <c r="B34" s="39" t="s">
         <v>365</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -3810,8 +3797,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="48"/>
-      <c r="B35" s="46"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="39"/>
       <c r="C35" s="1" t="s">
         <v>107</v>
       </c>
@@ -3824,8 +3811,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="48"/>
-      <c r="B36" s="46"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="39"/>
       <c r="C36" s="1" t="s">
         <v>84</v>
       </c>
@@ -3838,8 +3825,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="48"/>
-      <c r="B37" s="46"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="39"/>
       <c r="C37" s="1" t="s">
         <v>246</v>
       </c>
@@ -3852,8 +3839,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="48"/>
-      <c r="B38" s="46"/>
+      <c r="A38" s="41"/>
+      <c r="B38" s="39"/>
       <c r="C38" s="1" t="s">
         <v>370</v>
       </c>
@@ -3866,8 +3853,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="48"/>
-      <c r="B39" s="46"/>
+      <c r="A39" s="41"/>
+      <c r="B39" s="39"/>
       <c r="C39" s="1" t="s">
         <v>234</v>
       </c>
@@ -3880,8 +3867,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="48"/>
-      <c r="B40" s="46"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="39"/>
       <c r="C40" s="1" t="s">
         <v>141</v>
       </c>
@@ -3894,8 +3881,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="48"/>
-      <c r="B41" s="46"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="39"/>
       <c r="C41" s="1" t="s">
         <v>155</v>
       </c>
@@ -3908,8 +3895,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="48"/>
-      <c r="B42" s="46"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="39"/>
       <c r="C42" s="1" t="s">
         <v>161</v>
       </c>
@@ -3922,8 +3909,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="48"/>
-      <c r="B43" s="46"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="39"/>
       <c r="C43" s="1" t="s">
         <v>196</v>
       </c>
@@ -3936,8 +3923,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="48"/>
-      <c r="B44" s="46"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="39"/>
       <c r="C44" s="1" t="s">
         <v>167</v>
       </c>
@@ -3950,8 +3937,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="48"/>
-      <c r="B45" s="46"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="39"/>
       <c r="C45" s="1" t="s">
         <v>188</v>
       </c>
@@ -3964,18 +3951,15 @@
       </c>
     </row>
     <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="48"/>
-      <c r="B46" s="46"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
+      <c r="A46" s="41"/>
+      <c r="B46" s="39"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="47" t="s">
+      <c r="A47" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="B47" s="51" t="s">
+      <c r="B47" s="43" t="s">
         <v>3</v>
       </c>
       <c r="C47" s="12" t="s">
@@ -3984,433 +3968,433 @@
       <c r="D47" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="29"/>
+      <c r="E47" s="25"/>
       <c r="F47" s="12" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="48"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="14" t="s">
+      <c r="A48" s="41"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="E48" s="17"/>
-      <c r="F48" s="14" t="s">
+      <c r="E48" s="3"/>
+      <c r="F48" s="1" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="48"/>
-      <c r="B49" s="52"/>
-      <c r="C49" s="14" t="s">
+      <c r="A49" s="41"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D49" s="14" t="s">
+      <c r="D49" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="E49" s="18"/>
-      <c r="F49" s="14" t="s">
+      <c r="E49" s="4"/>
+      <c r="F49" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="48"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="14" t="s">
+      <c r="A50" s="41"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="14" t="s">
+      <c r="D50" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="E50" s="17"/>
-      <c r="F50" s="14" t="s">
+      <c r="E50" s="3"/>
+      <c r="F50" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="48"/>
-      <c r="B51" s="52"/>
-      <c r="C51" s="14" t="s">
+      <c r="A51" s="41"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D51" s="14" t="s">
+      <c r="D51" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="E51" s="17"/>
-      <c r="F51" s="14" t="s">
+      <c r="E51" s="3"/>
+      <c r="F51" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="48"/>
-      <c r="B52" s="52"/>
-      <c r="C52" s="14" t="s">
+      <c r="A52" s="41"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D52" s="14" t="s">
+      <c r="D52" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="E52" s="17"/>
-      <c r="F52" s="14" t="s">
+      <c r="E52" s="3"/>
+      <c r="F52" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="48"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="14" t="s">
+      <c r="A53" s="41"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D53" s="14" t="s">
+      <c r="D53" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E53" s="17"/>
-      <c r="F53" s="14" t="s">
+      <c r="E53" s="3"/>
+      <c r="F53" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="48"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="14" t="s">
+      <c r="A54" s="41"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D54" s="14" t="s">
+      <c r="D54" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="E54" s="17"/>
-      <c r="F54" s="14" t="s">
+      <c r="E54" s="3"/>
+      <c r="F54" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="48"/>
-      <c r="B55" s="52"/>
-      <c r="C55" s="14" t="s">
+      <c r="A55" s="41"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D55" s="14" t="s">
+      <c r="D55" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="E55" s="17"/>
-      <c r="F55" s="14" t="s">
+      <c r="E55" s="3"/>
+      <c r="F55" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="48"/>
-      <c r="B56" s="53"/>
-      <c r="C56" s="21"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="21"/>
+      <c r="A56" s="41"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="17"/>
+      <c r="D56" s="17"/>
+      <c r="E56" s="18"/>
+      <c r="F56" s="17"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="48"/>
-      <c r="B57" s="52" t="s">
+      <c r="A57" s="41"/>
+      <c r="B57" s="44" t="s">
         <v>278</v>
       </c>
-      <c r="C57" s="14" t="s">
+      <c r="C57" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D57" s="14" t="s">
+      <c r="D57" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="14" t="s">
+      <c r="E57" s="2"/>
+      <c r="F57" s="1" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="14" t="s">
+      <c r="A58" s="41"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="E58" s="17"/>
-      <c r="F58" s="14" t="s">
+      <c r="E58" s="3"/>
+      <c r="F58" s="1" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="48"/>
-      <c r="B59" s="52"/>
-      <c r="C59" s="14" t="s">
+      <c r="A59" s="41"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="E59" s="18"/>
-      <c r="F59" s="14" t="s">
+      <c r="E59" s="4"/>
+      <c r="F59" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="48"/>
-      <c r="B60" s="52"/>
-      <c r="C60" s="14" t="s">
+      <c r="A60" s="41"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D60" s="14" t="s">
+      <c r="D60" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="E60" s="17"/>
-      <c r="F60" s="14" t="s">
+      <c r="E60" s="3"/>
+      <c r="F60" s="1" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="48"/>
-      <c r="B61" s="52"/>
-      <c r="C61" s="14" t="s">
+      <c r="A61" s="41"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D61" s="14" t="s">
+      <c r="D61" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="E61" s="17"/>
-      <c r="F61" s="14" t="s">
+      <c r="E61" s="3"/>
+      <c r="F61" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="48"/>
-      <c r="B62" s="52"/>
-      <c r="C62" s="14" t="s">
+      <c r="A62" s="41"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D62" s="14" t="s">
+      <c r="D62" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="E62" s="17"/>
-      <c r="F62" s="14" t="s">
+      <c r="E62" s="3"/>
+      <c r="F62" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="48"/>
-      <c r="B63" s="52"/>
-      <c r="C63" s="14" t="s">
+      <c r="A63" s="41"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" s="1" t="s">
         <v>294</v>
       </c>
-      <c r="E63" s="17"/>
-      <c r="F63" s="14" t="s">
+      <c r="E63" s="3"/>
+      <c r="F63" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="48"/>
-      <c r="B64" s="52"/>
-      <c r="C64" s="14" t="s">
+      <c r="A64" s="41"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D64" s="14" t="s">
+      <c r="D64" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="E64" s="17"/>
-      <c r="F64" s="14" t="s">
+      <c r="E64" s="3"/>
+      <c r="F64" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="48"/>
-      <c r="B65" s="52"/>
-      <c r="C65" s="14" t="s">
+      <c r="A65" s="41"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="E65" s="17"/>
-      <c r="F65" s="14" t="s">
+      <c r="E65" s="3"/>
+      <c r="F65" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="48"/>
-      <c r="B66" s="53"/>
-      <c r="E66" s="17"/>
+      <c r="A66" s="41"/>
+      <c r="B66" s="45"/>
+      <c r="E66" s="3"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="48"/>
-      <c r="B67" s="54" t="s">
+      <c r="A67" s="41"/>
+      <c r="B67" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D67" s="19" t="s">
+      <c r="D67" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="23"/>
-      <c r="F67" s="19" t="s">
+      <c r="E67" s="19"/>
+      <c r="F67" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="48"/>
-      <c r="B68" s="52"/>
-      <c r="C68" s="14" t="s">
+      <c r="A68" s="41"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D68" s="14" t="s">
+      <c r="D68" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="E68" s="17"/>
-      <c r="F68" s="14" t="s">
+      <c r="E68" s="3"/>
+      <c r="F68" s="1" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="48"/>
-      <c r="B69" s="56"/>
-      <c r="C69" s="14" t="s">
+      <c r="A69" s="41"/>
+      <c r="B69" s="48"/>
+      <c r="C69" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D69" s="14" t="s">
+      <c r="D69" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E69" s="15"/>
-      <c r="F69" s="14" t="s">
+      <c r="E69" s="2"/>
+      <c r="F69" s="1" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="48"/>
-      <c r="B70" s="56"/>
-      <c r="C70" s="14" t="s">
+      <c r="A70" s="41"/>
+      <c r="B70" s="48"/>
+      <c r="C70" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D70" s="14" t="s">
+      <c r="D70" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="E70" s="15"/>
-      <c r="F70" s="14" t="s">
+      <c r="E70" s="2"/>
+      <c r="F70" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="48"/>
-      <c r="B71" s="56"/>
-      <c r="C71" s="14" t="s">
+      <c r="A71" s="41"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D71" s="14" t="s">
+      <c r="D71" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="14" t="s">
+      <c r="E71" s="2"/>
+      <c r="F71" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="48"/>
-      <c r="B72" s="56"/>
-      <c r="C72" s="14" t="s">
+      <c r="A72" s="41"/>
+      <c r="B72" s="48"/>
+      <c r="C72" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="D72" s="14" t="s">
+      <c r="D72" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="E72" s="17"/>
-      <c r="F72" s="14" t="s">
+      <c r="E72" s="3"/>
+      <c r="F72" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="48"/>
-      <c r="B73" s="56"/>
-      <c r="C73" s="14" t="s">
+      <c r="A73" s="41"/>
+      <c r="B73" s="48"/>
+      <c r="C73" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="E73" s="15"/>
-      <c r="F73" s="14" t="s">
+      <c r="E73" s="2"/>
+      <c r="F73" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="48"/>
-      <c r="B74" s="56"/>
-      <c r="C74" s="14" t="s">
+      <c r="A74" s="41"/>
+      <c r="B74" s="48"/>
+      <c r="C74" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D74" s="14" t="s">
+      <c r="D74" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E74" s="17"/>
-      <c r="F74" s="14" t="s">
+      <c r="E74" s="3"/>
+      <c r="F74" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="48"/>
-      <c r="B75" s="56"/>
-      <c r="C75" s="14" t="s">
+      <c r="A75" s="41"/>
+      <c r="B75" s="48"/>
+      <c r="C75" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D75" s="14" t="s">
+      <c r="D75" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="E75" s="17"/>
-      <c r="F75" s="14" t="s">
+      <c r="E75" s="3"/>
+      <c r="F75" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="48"/>
-      <c r="B76" s="56"/>
-      <c r="C76" s="14" t="s">
+      <c r="A76" s="41"/>
+      <c r="B76" s="48"/>
+      <c r="C76" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E76" s="17"/>
-      <c r="F76" s="14" t="s">
+      <c r="E76" s="3"/>
+      <c r="F76" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="48"/>
-      <c r="B77" s="56"/>
-      <c r="C77" s="14" t="s">
+      <c r="A77" s="41"/>
+      <c r="B77" s="48"/>
+      <c r="C77" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D77" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="E77" s="17"/>
-      <c r="F77" s="14" t="s">
+      <c r="E77" s="3"/>
+      <c r="F77" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="49"/>
-      <c r="B78" s="57"/>
-      <c r="C78" s="31"/>
-      <c r="D78" s="31"/>
-      <c r="E78" s="32"/>
-      <c r="F78" s="31"/>
+      <c r="A78" s="42"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="28"/>
+      <c r="F78" s="27"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="47" t="s">
+      <c r="A79" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="B79" s="58" t="s">
+      <c r="B79" s="50" t="s">
         <v>73</v>
       </c>
       <c r="C79" s="12" t="s">
@@ -4419,36 +4403,36 @@
       <c r="D79" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="E79" s="29"/>
+      <c r="E79" s="25"/>
       <c r="F79" s="12" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="48"/>
-      <c r="B80" s="61"/>
-      <c r="C80" s="39" t="s">
+      <c r="A80" s="41"/>
+      <c r="B80" s="48"/>
+      <c r="C80" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="D80" s="39" t="s">
+      <c r="D80" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="E80" s="41"/>
-      <c r="F80" s="39" t="s">
+      <c r="E80" s="2"/>
+      <c r="F80" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="48"/>
-      <c r="B81" s="60"/>
-      <c r="C81" s="21"/>
-      <c r="D81" s="21"/>
-      <c r="E81" s="45"/>
-      <c r="F81" s="21"/>
-    </row>
-    <row r="82" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="48"/>
-      <c r="B82" s="63" t="s">
+      <c r="A81" s="41"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="17"/>
+      <c r="D81" s="17"/>
+      <c r="E81" s="38"/>
+      <c r="F81" s="17"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="41"/>
+      <c r="B82" s="53" t="s">
         <v>380</v>
       </c>
       <c r="C82" s="1" t="s">
@@ -4462,9 +4446,9 @@
         <v>383</v>
       </c>
     </row>
-    <row r="83" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="48"/>
-      <c r="B83" s="63"/>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="41"/>
+      <c r="B83" s="53"/>
       <c r="C83" s="1" t="s">
         <v>384</v>
       </c>
@@ -4476,280 +4460,280 @@
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="48"/>
-      <c r="B84" s="63"/>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="41"/>
+      <c r="B84" s="53"/>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="48"/>
-      <c r="B85" s="54" t="s">
+      <c r="A85" s="41"/>
+      <c r="B85" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C85" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D85" s="19" t="s">
+      <c r="D85" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="E85" s="23"/>
-      <c r="F85" s="19" t="s">
+      <c r="E85" s="19"/>
+      <c r="F85" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="48"/>
-      <c r="B86" s="52"/>
-      <c r="C86" s="14" t="s">
+      <c r="A86" s="41"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D86" s="14" t="s">
+      <c r="D86" s="1" t="s">
         <v>109</v>
       </c>
       <c r="E86" s="5"/>
-      <c r="F86" s="14" t="s">
+      <c r="F86" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="48"/>
-      <c r="B87" s="52"/>
-      <c r="C87" s="14" t="s">
+      <c r="A87" s="41"/>
+      <c r="B87" s="44"/>
+      <c r="C87" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D87" s="14" t="s">
+      <c r="D87" s="1" t="s">
         <v>121</v>
       </c>
       <c r="E87" s="5"/>
-      <c r="F87" s="14" t="s">
+      <c r="F87" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="48"/>
-      <c r="B88" s="52"/>
-      <c r="C88" s="14" t="s">
+      <c r="A88" s="41"/>
+      <c r="B88" s="44"/>
+      <c r="C88" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D88" s="14" t="s">
+      <c r="D88" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E88" s="15"/>
-      <c r="F88" s="14" t="s">
+      <c r="E88" s="2"/>
+      <c r="F88" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="48"/>
-      <c r="B89" s="52"/>
-      <c r="C89" s="14" t="s">
+      <c r="A89" s="41"/>
+      <c r="B89" s="44"/>
+      <c r="C89" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D89" s="14" t="s">
+      <c r="D89" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="E89" s="18"/>
-      <c r="F89" s="14" t="s">
+      <c r="E89" s="4"/>
+      <c r="F89" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="48"/>
-      <c r="B90" s="52"/>
-      <c r="C90" s="14" t="s">
+      <c r="A90" s="41"/>
+      <c r="B90" s="44"/>
+      <c r="C90" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D90" s="14" t="s">
+      <c r="D90" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E90" s="15"/>
-      <c r="F90" s="14" t="s">
+      <c r="E90" s="2"/>
+      <c r="F90" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="48"/>
-      <c r="B91" s="52"/>
-      <c r="C91" s="14" t="s">
+      <c r="A91" s="41"/>
+      <c r="B91" s="44"/>
+      <c r="C91" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D91" s="14" t="s">
+      <c r="D91" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E91" s="15"/>
-      <c r="F91" s="14" t="s">
+      <c r="E91" s="2"/>
+      <c r="F91" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="48"/>
-      <c r="B92" s="52"/>
-      <c r="C92" s="14" t="s">
+      <c r="A92" s="41"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D92" s="14" t="s">
+      <c r="D92" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="E92" s="17"/>
-      <c r="F92" s="14" t="s">
+      <c r="E92" s="3"/>
+      <c r="F92" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="48"/>
-      <c r="B93" s="52"/>
-      <c r="C93" s="14" t="s">
+      <c r="A93" s="41"/>
+      <c r="B93" s="44"/>
+      <c r="C93" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D93" s="14" t="s">
+      <c r="D93" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E93" s="17"/>
-      <c r="F93" s="14" t="s">
+      <c r="E93" s="3"/>
+      <c r="F93" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="48"/>
-      <c r="B94" s="53"/>
+      <c r="A94" s="41"/>
+      <c r="B94" s="45"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="48"/>
-      <c r="B95" s="54" t="s">
+      <c r="A95" s="41"/>
+      <c r="B95" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C95" s="19" t="s">
+      <c r="C95" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="D95" s="19" t="s">
+      <c r="D95" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="E95" s="23"/>
-      <c r="F95" s="19" t="s">
+      <c r="E95" s="19"/>
+      <c r="F95" s="15" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="48"/>
-      <c r="B96" s="52"/>
-      <c r="C96" s="14" t="s">
+      <c r="A96" s="41"/>
+      <c r="B96" s="44"/>
+      <c r="C96" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D96" s="14" t="s">
+      <c r="D96" s="1" t="s">
         <v>106</v>
       </c>
       <c r="E96" s="5"/>
-      <c r="F96" s="14" t="s">
+      <c r="F96" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="48"/>
-      <c r="B97" s="52"/>
-      <c r="C97" s="14" t="s">
+      <c r="A97" s="41"/>
+      <c r="B97" s="44"/>
+      <c r="C97" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D97" s="14" t="s">
+      <c r="D97" s="1" t="s">
         <v>119</v>
       </c>
       <c r="E97" s="5"/>
-      <c r="F97" s="14" t="s">
+      <c r="F97" s="1" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="48"/>
-      <c r="B98" s="52"/>
-      <c r="C98" s="14" t="s">
+      <c r="A98" s="41"/>
+      <c r="B98" s="44"/>
+      <c r="C98" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="D98" s="14" t="s">
+      <c r="D98" s="1" t="s">
         <v>142</v>
       </c>
       <c r="E98" s="5"/>
-      <c r="F98" s="14" t="s">
+      <c r="F98" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="48"/>
-      <c r="B99" s="52"/>
-      <c r="C99" s="14" t="s">
+      <c r="A99" s="41"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D99" s="14" t="s">
+      <c r="D99" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="E99" s="18"/>
-      <c r="F99" s="14" t="s">
+      <c r="E99" s="4"/>
+      <c r="F99" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="48"/>
-      <c r="B100" s="52"/>
-      <c r="C100" s="14" t="s">
+      <c r="A100" s="41"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D100" s="14" t="s">
+      <c r="D100" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="E100" s="33"/>
-      <c r="F100" s="14" t="s">
+      <c r="E100" s="29"/>
+      <c r="F100" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="48"/>
-      <c r="B101" s="52"/>
-      <c r="C101" s="14" t="s">
+      <c r="A101" s="41"/>
+      <c r="B101" s="44"/>
+      <c r="C101" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="D101" s="14" t="s">
+      <c r="D101" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="E101" s="33"/>
-      <c r="F101" s="14" t="s">
+      <c r="E101" s="29"/>
+      <c r="F101" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="48"/>
-      <c r="B102" s="52"/>
-      <c r="C102" s="14" t="s">
+      <c r="A102" s="41"/>
+      <c r="B102" s="44"/>
+      <c r="C102" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D102" s="14" t="s">
+      <c r="D102" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E102" s="17"/>
-      <c r="F102" s="14" t="s">
+      <c r="E102" s="3"/>
+      <c r="F102" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="48"/>
-      <c r="B103" s="52"/>
-      <c r="C103" s="14" t="s">
+      <c r="A103" s="41"/>
+      <c r="B103" s="44"/>
+      <c r="C103" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D103" s="14" t="s">
+      <c r="D103" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E103" s="17"/>
-      <c r="F103" s="14" t="s">
+      <c r="E103" s="3"/>
+      <c r="F103" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="49"/>
-      <c r="B104" s="55"/>
+      <c r="A104" s="42"/>
+      <c r="B104" s="47"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="47" t="s">
+      <c r="A105" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="B105" s="58" t="s">
+      <c r="B105" s="50" t="s">
         <v>73</v>
       </c>
       <c r="C105" s="12" t="s">
@@ -4764,209 +4748,209 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="48"/>
-      <c r="B106" s="56"/>
-      <c r="C106" s="14" t="s">
+      <c r="A106" s="41"/>
+      <c r="B106" s="48"/>
+      <c r="C106" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="D106" s="14" t="s">
+      <c r="D106" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="E106" s="17"/>
-      <c r="F106" s="14" t="s">
+      <c r="E106" s="3"/>
+      <c r="F106" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="48"/>
-      <c r="B107" s="56"/>
-      <c r="C107" s="14" t="s">
+      <c r="A107" s="41"/>
+      <c r="B107" s="48"/>
+      <c r="C107" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="D107" s="14" t="s">
+      <c r="D107" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="E107" s="17"/>
-      <c r="F107" s="14" t="s">
+      <c r="E107" s="3"/>
+      <c r="F107" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="48"/>
-      <c r="B108" s="60"/>
-      <c r="C108" s="21"/>
-      <c r="D108" s="21"/>
-      <c r="E108" s="22"/>
-      <c r="F108" s="21"/>
+      <c r="A108" s="41"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="17"/>
+      <c r="D108" s="17"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="17"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="48"/>
-      <c r="B109" s="59" t="s">
+      <c r="A109" s="41"/>
+      <c r="B109" s="51" t="s">
         <v>265</v>
       </c>
-      <c r="C109" s="14" t="s">
+      <c r="C109" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="D109" s="14" t="s">
+      <c r="D109" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="E109" s="17"/>
-      <c r="F109" s="14" t="s">
+      <c r="E109" s="3"/>
+      <c r="F109" s="1" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="48"/>
-      <c r="B110" s="56"/>
-      <c r="C110" s="14" t="s">
+      <c r="A110" s="41"/>
+      <c r="B110" s="48"/>
+      <c r="C110" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="D110" s="14" t="s">
+      <c r="D110" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="E110" s="17"/>
-      <c r="F110" s="14" t="s">
+      <c r="E110" s="3"/>
+      <c r="F110" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="48"/>
-      <c r="B111" s="56"/>
-      <c r="C111" s="14" t="s">
+      <c r="A111" s="41"/>
+      <c r="B111" s="48"/>
+      <c r="C111" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="D111" s="14" t="s">
+      <c r="D111" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="E111" s="17"/>
-      <c r="F111" s="14" t="s">
+      <c r="E111" s="3"/>
+      <c r="F111" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="48"/>
-      <c r="B112" s="60"/>
-      <c r="E112" s="17"/>
+      <c r="A112" s="41"/>
+      <c r="B112" s="52"/>
+      <c r="E112" s="3"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="48"/>
-      <c r="B113" s="59" t="s">
+      <c r="A113" s="41"/>
+      <c r="B113" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="C113" s="19" t="s">
+      <c r="C113" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="D113" s="19" t="s">
+      <c r="D113" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E113" s="23"/>
-      <c r="F113" s="19" t="s">
+      <c r="E113" s="19"/>
+      <c r="F113" s="15" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="48"/>
-      <c r="B114" s="61"/>
-      <c r="C114" s="39" t="s">
+      <c r="A114" s="41"/>
+      <c r="B114" s="48"/>
+      <c r="C114" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="D114" s="39" t="s">
+      <c r="D114" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E114" s="40"/>
-      <c r="F114" s="39" t="s">
+      <c r="E114" s="3"/>
+      <c r="F114" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="48"/>
-      <c r="B115" s="60"/>
-      <c r="C115" s="21"/>
-      <c r="D115" s="21"/>
-      <c r="E115" s="22"/>
-      <c r="F115" s="21"/>
+      <c r="A115" s="41"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="17"/>
+      <c r="D115" s="17"/>
+      <c r="E115" s="18"/>
+      <c r="F115" s="17"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="48"/>
-      <c r="B116" s="59" t="s">
+      <c r="A116" s="41"/>
+      <c r="B116" s="51" t="s">
         <v>344</v>
       </c>
-      <c r="C116" s="19" t="s">
+      <c r="C116" s="15" t="s">
         <v>348</v>
       </c>
-      <c r="D116" s="19" t="s">
+      <c r="D116" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="E116" s="23"/>
-      <c r="F116" s="19" t="s">
+      <c r="E116" s="19"/>
+      <c r="F116" s="15" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="48"/>
-      <c r="B117" s="61"/>
-      <c r="C117" s="39" t="s">
+      <c r="A117" s="41"/>
+      <c r="B117" s="48"/>
+      <c r="C117" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="D117" s="39" t="s">
+      <c r="D117" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="E117" s="40"/>
-      <c r="F117" s="39" t="s">
+      <c r="E117" s="3"/>
+      <c r="F117" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="48"/>
-      <c r="B118" s="60"/>
-      <c r="C118" s="21"/>
-      <c r="D118" s="21"/>
-      <c r="E118" s="22"/>
-      <c r="F118" s="21"/>
+      <c r="A118" s="41"/>
+      <c r="B118" s="52"/>
+      <c r="C118" s="17"/>
+      <c r="D118" s="17"/>
+      <c r="E118" s="18"/>
+      <c r="F118" s="17"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="48"/>
-      <c r="B119" s="61" t="s">
+      <c r="A119" s="41"/>
+      <c r="B119" s="48" t="s">
         <v>304</v>
       </c>
-      <c r="C119" s="14" t="s">
+      <c r="C119" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="D119" s="14" t="s">
+      <c r="D119" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="E119" s="17"/>
-      <c r="F119" s="14" t="s">
+      <c r="E119" s="3"/>
+      <c r="F119" s="1" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="48"/>
-      <c r="B120" s="56"/>
-      <c r="C120" s="14" t="s">
+      <c r="A120" s="41"/>
+      <c r="B120" s="48"/>
+      <c r="C120" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="D120" s="14" t="s">
+      <c r="D120" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="E120" s="17"/>
-      <c r="F120" s="14" t="s">
+      <c r="E120" s="3"/>
+      <c r="F120" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="49"/>
-      <c r="B121" s="57"/>
-      <c r="C121" s="31"/>
-      <c r="D121" s="31"/>
-      <c r="E121" s="32"/>
-      <c r="F121" s="31"/>
+      <c r="A121" s="42"/>
+      <c r="B121" s="49"/>
+      <c r="C121" s="27"/>
+      <c r="D121" s="27"/>
+      <c r="E121" s="28"/>
+      <c r="F121" s="27"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="47" t="s">
+      <c r="A122" s="40" t="s">
         <v>163</v>
       </c>
-      <c r="B122" s="58" t="s">
+      <c r="B122" s="50" t="s">
         <v>13</v>
       </c>
       <c r="C122" s="12" t="s">
@@ -4981,426 +4965,411 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="50"/>
-      <c r="B123" s="61"/>
-      <c r="C123" s="14" t="s">
+      <c r="A123" s="41"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D123" s="14" t="s">
+      <c r="D123" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="F123" s="14" t="s">
+      <c r="F123" s="1" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="50"/>
-      <c r="B124" s="60"/>
-      <c r="C124" s="21"/>
-      <c r="D124" s="21"/>
-      <c r="E124" s="21"/>
-      <c r="F124" s="21"/>
+      <c r="A124" s="41"/>
+      <c r="B124" s="52"/>
+      <c r="C124" s="17"/>
+      <c r="D124" s="17"/>
+      <c r="E124" s="17"/>
+      <c r="F124" s="17"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="50"/>
-      <c r="B125" s="59" t="s">
+      <c r="A125" s="41"/>
+      <c r="B125" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="C125" s="14" t="s">
+      <c r="C125" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D125" s="14" t="s">
+      <c r="D125" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F125" s="14" t="s">
+      <c r="F125" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="50"/>
-      <c r="B126" s="61"/>
-      <c r="C126" s="14" t="s">
+      <c r="A126" s="41"/>
+      <c r="B126" s="48"/>
+      <c r="C126" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="D126" s="14" t="s">
+      <c r="D126" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="F126" s="14" t="s">
+      <c r="F126" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="50"/>
-      <c r="B127" s="61"/>
-      <c r="C127" s="14" t="s">
+      <c r="A127" s="41"/>
+      <c r="B127" s="48"/>
+      <c r="C127" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="D127" s="14" t="s">
+      <c r="D127" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F127" s="14" t="s">
+      <c r="F127" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="50"/>
-      <c r="B128" s="61"/>
-      <c r="C128" s="14" t="s">
+      <c r="A128" s="41"/>
+      <c r="B128" s="48"/>
+      <c r="C128" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="D128" s="14" t="s">
+      <c r="D128" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F128" s="14" t="s">
+      <c r="F128" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="50"/>
-      <c r="B129" s="61"/>
-      <c r="C129" s="14" t="s">
+      <c r="A129" s="41"/>
+      <c r="B129" s="48"/>
+      <c r="C129" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="D129" s="14" t="s">
+      <c r="D129" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F129" s="14" t="s">
+      <c r="F129" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="50"/>
-      <c r="B130" s="61"/>
-      <c r="C130" s="14" t="s">
+      <c r="A130" s="41"/>
+      <c r="B130" s="48"/>
+      <c r="C130" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="D130" s="14" t="s">
+      <c r="D130" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="F130" s="14" t="s">
+      <c r="F130" s="1" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="50"/>
-      <c r="B131" s="60"/>
+      <c r="A131" s="41"/>
+      <c r="B131" s="52"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="50"/>
-      <c r="B132" s="59" t="s">
+      <c r="A132" s="41"/>
+      <c r="B132" s="51" t="s">
         <v>206</v>
       </c>
-      <c r="C132" s="19" t="s">
+      <c r="C132" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="D132" s="19" t="s">
+      <c r="D132" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="E132" s="19"/>
-      <c r="F132" s="19" t="s">
+      <c r="E132" s="15"/>
+      <c r="F132" s="15" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="50"/>
-      <c r="B133" s="61"/>
-      <c r="C133" s="14" t="s">
+      <c r="A133" s="41"/>
+      <c r="B133" s="48"/>
+      <c r="C133" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="D133" s="14" t="s">
+      <c r="D133" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F133" s="14" t="s">
+      <c r="F133" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="50"/>
-      <c r="B134" s="61"/>
-      <c r="C134" s="14" t="s">
+      <c r="A134" s="41"/>
+      <c r="B134" s="48"/>
+      <c r="C134" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="D134" s="14" t="s">
+      <c r="D134" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F134" s="14" t="s">
+      <c r="F134" s="1" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="50"/>
-      <c r="B135" s="61"/>
-      <c r="C135" s="14" t="s">
+      <c r="A135" s="41"/>
+      <c r="B135" s="48"/>
+      <c r="C135" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="D135" s="14" t="s">
+      <c r="D135" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="F135" s="14" t="s">
+      <c r="F135" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="50"/>
-      <c r="B136" s="61"/>
-      <c r="C136" s="14" t="s">
+      <c r="A136" s="41"/>
+      <c r="B136" s="48"/>
+      <c r="C136" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="D136" s="14" t="s">
+      <c r="D136" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="F136" s="14" t="s">
+      <c r="F136" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="50"/>
-      <c r="B137" s="61"/>
-      <c r="C137" s="14" t="s">
+      <c r="A137" s="41"/>
+      <c r="B137" s="48"/>
+      <c r="C137" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D137" s="14" t="s">
+      <c r="D137" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="F137" s="14" t="s">
+      <c r="F137" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="50"/>
-      <c r="B138" s="61"/>
-      <c r="C138" s="14" t="s">
+      <c r="A138" s="41"/>
+      <c r="B138" s="48"/>
+      <c r="C138" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="D138" s="14" t="s">
+      <c r="D138" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="F138" s="14" t="s">
+      <c r="F138" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="50"/>
-      <c r="B139" s="61"/>
-      <c r="C139" s="14" t="s">
+      <c r="A139" s="41"/>
+      <c r="B139" s="48"/>
+      <c r="C139" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="D139" s="14" t="s">
+      <c r="D139" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="F139" s="14" t="s">
+      <c r="F139" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="50"/>
-      <c r="B140" s="61"/>
-      <c r="C140" s="14" t="s">
+      <c r="A140" s="41"/>
+      <c r="B140" s="48"/>
+      <c r="C140" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="D140" s="14" t="s">
+      <c r="D140" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="F140" s="14" t="s">
+      <c r="F140" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="50"/>
-      <c r="B141" s="61"/>
-      <c r="C141" s="14" t="s">
+      <c r="A141" s="41"/>
+      <c r="B141" s="48"/>
+      <c r="C141" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="D141" s="14" t="s">
+      <c r="D141" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="F141" s="14" t="s">
+      <c r="F141" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="50"/>
-      <c r="B142" s="61"/>
-      <c r="C142" s="14" t="s">
+      <c r="A142" s="41"/>
+      <c r="B142" s="48"/>
+      <c r="C142" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="D142" s="14" t="s">
+      <c r="D142" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F142" s="14" t="s">
+      <c r="F142" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="50"/>
-      <c r="B143" s="61"/>
-      <c r="C143" s="14" t="s">
+      <c r="A143" s="41"/>
+      <c r="B143" s="48"/>
+      <c r="C143" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="D143" s="14" t="s">
+      <c r="D143" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="F143" s="14" t="s">
+      <c r="F143" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="50"/>
-      <c r="B144" s="61"/>
-      <c r="C144" s="14" t="s">
+      <c r="A144" s="41"/>
+      <c r="B144" s="48"/>
+      <c r="C144" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="D144" s="14" t="s">
+      <c r="D144" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F144" s="14" t="s">
+      <c r="F144" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="50"/>
-      <c r="B145" s="61"/>
-      <c r="C145" s="14" t="s">
+      <c r="A145" s="41"/>
+      <c r="B145" s="48"/>
+      <c r="C145" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="D145" s="14" t="s">
+      <c r="D145" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="F145" s="14" t="s">
+      <c r="F145" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="50"/>
-      <c r="B146" s="60"/>
+      <c r="A146" s="41"/>
+      <c r="B146" s="52"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="50"/>
-      <c r="B147" s="59" t="s">
+      <c r="A147" s="41"/>
+      <c r="B147" s="51" t="s">
         <v>222</v>
       </c>
-      <c r="C147" s="19" t="s">
+      <c r="C147" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="D147" s="19" t="s">
+      <c r="D147" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E147" s="19"/>
-      <c r="F147" s="19" t="s">
+      <c r="E147" s="15"/>
+      <c r="F147" s="15" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="50"/>
-      <c r="B148" s="61"/>
-      <c r="C148" s="39" t="s">
+      <c r="A148" s="41"/>
+      <c r="B148" s="48"/>
+      <c r="C148" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="D148" s="39" t="s">
+      <c r="D148" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="E148" s="39"/>
-      <c r="F148" s="39" t="s">
+      <c r="F148" s="1" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="50"/>
-      <c r="B149" s="61"/>
-      <c r="C149" s="39" t="s">
+      <c r="A149" s="41"/>
+      <c r="B149" s="48"/>
+      <c r="C149" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="D149" s="39" t="s">
+      <c r="D149" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="E149" s="39"/>
-      <c r="F149" s="39" t="s">
+      <c r="F149" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="50"/>
-      <c r="B150" s="61"/>
-      <c r="C150" s="39" t="s">
+      <c r="A150" s="41"/>
+      <c r="B150" s="48"/>
+      <c r="C150" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="D150" s="39" t="s">
+      <c r="D150" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="E150" s="39"/>
-      <c r="F150" s="39" t="s">
+      <c r="F150" s="1" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="50"/>
-      <c r="B151" s="61"/>
-      <c r="C151" s="39" t="s">
+      <c r="A151" s="41"/>
+      <c r="B151" s="48"/>
+      <c r="C151" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="D151" s="39" t="s">
+      <c r="D151" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="E151" s="39"/>
-      <c r="F151" s="39" t="s">
+      <c r="F151" s="1" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="50"/>
-      <c r="B152" s="60"/>
-      <c r="C152" s="21"/>
-      <c r="D152" s="21"/>
-      <c r="E152" s="21"/>
-      <c r="F152" s="21"/>
+      <c r="A152" s="41"/>
+      <c r="B152" s="52"/>
+      <c r="C152" s="17"/>
+      <c r="D152" s="17"/>
+      <c r="E152" s="17"/>
+      <c r="F152" s="17"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="50"/>
-      <c r="B153" s="62" t="s">
+      <c r="A153" s="41"/>
+      <c r="B153" s="54" t="s">
         <v>359</v>
       </c>
-      <c r="C153" s="39" t="s">
+      <c r="C153" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="D153" s="39" t="s">
+      <c r="D153" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="E153" s="39"/>
-      <c r="F153" s="39" t="s">
+      <c r="F153" s="1" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="50"/>
-      <c r="B154" s="62"/>
-      <c r="C154" s="39" t="s">
+      <c r="A154" s="41"/>
+      <c r="B154" s="54"/>
+      <c r="C154" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="D154" s="39" t="s">
+      <c r="D154" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="E154" s="39"/>
-      <c r="F154" s="39" t="s">
+      <c r="F154" s="1" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C155" s="39"/>
-      <c r="D155" s="39"/>
-      <c r="E155" s="39"/>
-      <c r="F155" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A2:A46"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="A47:A78"/>
-    <mergeCell ref="B67:B78"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B47:B56"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="B34:B46"/>
+    <mergeCell ref="B147:B152"/>
+    <mergeCell ref="B153:B154"/>
+    <mergeCell ref="A122:A154"/>
+    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="B132:B146"/>
+    <mergeCell ref="B125:B131"/>
     <mergeCell ref="B119:B121"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="A79:A104"/>
@@ -5412,12 +5381,15 @@
     <mergeCell ref="B113:B115"/>
     <mergeCell ref="B116:B118"/>
     <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B147:B152"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="A122:A154"/>
-    <mergeCell ref="B122:B124"/>
-    <mergeCell ref="B132:B146"/>
-    <mergeCell ref="B125:B131"/>
+    <mergeCell ref="A2:A46"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="A47:A78"/>
+    <mergeCell ref="B67:B78"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B47:B56"/>
+    <mergeCell ref="B57:B66"/>
+    <mergeCell ref="B34:B46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Fischer_Tropsch/FischerTropsch_Naphta_Bio_Brownfield_Memmingen/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Naphta_Bio_Brownfield_Memmingen/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Bio_Brownfield_Memmingen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Naphta_Bio_Brownfield_Memmingen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{787619BA-4D9A-4139-96D5-01FAE47C5BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D7B6C4-B2C5-445E-B2F4-F6CBDFD72526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-2400" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -162,7 +162,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="403">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -847,12 +847,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>kWh/kg_CO2</t>
   </si>
   <si>
@@ -970,13 +964,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1392,10 +1380,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -1555,46 +1543,46 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1645,11 +1633,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2118,19 +2106,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="41"/>
       <c r="B8" s="51" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="E8" s="16">
         <v>38.99</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2140,7 +2128,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E9" s="2">
         <v>285.39999999999998</v>
@@ -2156,13 +2144,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E10" s="2">
         <v>2440</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2172,7 +2160,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="E11" s="3">
         <v>0.03</v>
@@ -2188,45 +2176,45 @@
         <v>86</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E12" s="2">
         <v>0.63</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="41"/>
       <c r="B13" s="48"/>
       <c r="C13" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="E13" s="2">
         <v>4.8600000000000003</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="41"/>
       <c r="B14" s="48"/>
       <c r="C14" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E14" s="2">
         <v>0.39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -2236,7 +2224,7 @@
         <v>13</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="E15" s="4">
         <v>20</v>
@@ -2252,7 +2240,7 @@
         <v>15</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E16" s="18">
         <v>7.0000000000000007E-2</v>
@@ -2264,13 +2252,13 @@
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="41"/>
       <c r="B17" s="51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C17" s="15" t="s">
         <v>8</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E17" s="19">
         <v>3.7</v>
@@ -2286,13 +2274,13 @@
         <v>84</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E18" s="3">
         <v>0.27</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2302,13 +2290,13 @@
         <v>10</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E19" s="3">
         <v>700</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2318,7 +2306,7 @@
         <v>11</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E20" s="3">
         <v>0.02</v>
@@ -2334,7 +2322,7 @@
         <v>13</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E21" s="3">
         <v>20</v>
@@ -2350,7 +2338,7 @@
         <v>15</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E22" s="18">
         <v>0.05</v>
@@ -2362,35 +2350,35 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="41"/>
       <c r="B23" s="39" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>84</v>
       </c>
       <c r="D23" s="35" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E23" s="11">
         <v>0.2</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="41"/>
       <c r="B24" s="39"/>
       <c r="C24" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D24" s="35" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E24" s="11">
         <v>0.92800000000000005</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -2400,23 +2388,23 @@
         <v>10</v>
       </c>
       <c r="D25" s="35" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E25" s="11">
         <v>1640</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="41"/>
       <c r="B26" s="39"/>
       <c r="C26" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D26" s="35" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="E26" s="10">
         <v>0.04</v>
@@ -2429,48 +2417,48 @@
       <c r="A27" s="41"/>
       <c r="B27" s="39"/>
       <c r="C27" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D27" s="35" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E27" s="10">
         <v>2.5</v>
       </c>
       <c r="F27" s="35" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="41"/>
       <c r="B28" s="39"/>
       <c r="C28" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E28" s="7">
         <v>1.5</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="41"/>
       <c r="B29" s="39"/>
       <c r="C29" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E29" s="7">
         <v>1.5E-3</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -2480,7 +2468,7 @@
         <v>13</v>
       </c>
       <c r="D30" s="35" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="E30" s="9">
         <v>25</v>
@@ -2496,7 +2484,7 @@
         <v>15</v>
       </c>
       <c r="D31" s="35" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="E31" s="10">
         <v>0.08</v>
@@ -2640,19 +2628,19 @@
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="41"/>
       <c r="B40" s="46" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C40" s="12" t="s">
         <v>87</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E40" s="25">
         <v>2.83</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2662,7 +2650,7 @@
         <v>11</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="E41" s="3">
         <v>0.03</v>
@@ -2678,7 +2666,7 @@
         <v>13</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E42" s="4">
         <v>30</v>
@@ -2694,7 +2682,7 @@
         <v>20</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="E43" s="3">
         <v>7.3999999999999999E-4</v>
@@ -2710,7 +2698,7 @@
         <v>35</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E44" s="3">
         <v>0.98</v>
@@ -2726,7 +2714,7 @@
         <v>36</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E45" s="3">
         <v>0.98</v>
@@ -2742,7 +2730,7 @@
         <v>15</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="E46" s="3">
         <v>0.05</v>
@@ -2758,7 +2746,7 @@
         <v>88</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="E47" s="18">
         <v>0</v>
@@ -2953,13 +2941,13 @@
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="41"/>
       <c r="B59" s="36" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D59" s="35" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E59" s="10">
         <v>0</v>
@@ -3210,7 +3198,7 @@
         <v>78</v>
       </c>
       <c r="E74" s="32">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F74" s="31" t="s">
         <v>19</v>
@@ -3219,19 +3207,19 @@
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="41"/>
       <c r="B75" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="C75" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>263</v>
-      </c>
       <c r="E75" s="3">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3255,38 +3243,38 @@
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="41"/>
       <c r="B77" s="33" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="E77" s="34">
         <v>-0.55000000000000004</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="42"/>
       <c r="B78" s="22" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C78" s="27" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E78" s="28">
         <f>-2.2</f>
         <v>-2.2000000000000002</v>
       </c>
       <c r="F78" s="27" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3313,7 +3301,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
@@ -3483,13 +3471,13 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="41"/>
       <c r="B12" s="51" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="15" t="s">
@@ -3500,28 +3488,28 @@
       <c r="A13" s="41"/>
       <c r="B13" s="48"/>
       <c r="C13" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="41"/>
       <c r="B14" s="48"/>
       <c r="C14" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -3531,7 +3519,7 @@
         <v>139</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2" t="s">
@@ -3542,14 +3530,14 @@
       <c r="A16" s="41"/>
       <c r="B16" s="48"/>
       <c r="C16" s="1" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -3559,7 +3547,7 @@
         <v>84</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" s="1" t="s">
@@ -3573,7 +3561,7 @@
         <v>141</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" s="1" t="s">
@@ -3587,7 +3575,7 @@
         <v>155</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="1" t="s">
@@ -3601,7 +3589,7 @@
         <v>196</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E20" s="4"/>
       <c r="F20" s="1" t="s">
@@ -3615,7 +3603,7 @@
         <v>167</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E21" s="4"/>
       <c r="F21" s="1" t="s">
@@ -3629,7 +3617,7 @@
         <v>188</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E22" s="4"/>
       <c r="F22" s="1" t="s">
@@ -3647,17 +3635,17 @@
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="41"/>
       <c r="B24" s="51" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
@@ -3667,7 +3655,7 @@
         <v>107</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="1" t="s">
@@ -3681,25 +3669,25 @@
         <v>84</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E26" s="3"/>
       <c r="F26" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="41"/>
       <c r="B27" s="48"/>
       <c r="C27" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E27" s="4"/>
       <c r="F27" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
@@ -3709,7 +3697,7 @@
         <v>141</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E28" s="4"/>
       <c r="F28" s="1" t="s">
@@ -3723,7 +3711,7 @@
         <v>155</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E29" s="4"/>
       <c r="F29" s="1" t="s">
@@ -3737,7 +3725,7 @@
         <v>196</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E30" s="4"/>
       <c r="F30" s="1" t="s">
@@ -3751,7 +3739,7 @@
         <v>167</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E31" s="3"/>
       <c r="F31" s="1" t="s">
@@ -3765,7 +3753,7 @@
         <v>188</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E32" s="3"/>
       <c r="F32" s="1" t="s">
@@ -3783,13 +3771,13 @@
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="41"/>
       <c r="B34" s="39" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>96</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="1" t="s">
@@ -3803,7 +3791,7 @@
         <v>107</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="1" t="s">
@@ -3817,7 +3805,7 @@
         <v>84</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E36" s="3"/>
       <c r="F36" s="1" t="s">
@@ -3828,42 +3816,42 @@
       <c r="A37" s="41"/>
       <c r="B37" s="39"/>
       <c r="C37" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E37" s="3"/>
       <c r="F37" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="41"/>
       <c r="B38" s="39"/>
       <c r="C38" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E38" s="3"/>
       <c r="F38" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="41"/>
       <c r="B39" s="39"/>
       <c r="C39" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E39" s="4"/>
       <c r="F39" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -3873,7 +3861,7 @@
         <v>141</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E40" s="4"/>
       <c r="F40" s="1" t="s">
@@ -3887,7 +3875,7 @@
         <v>155</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E41" s="4"/>
       <c r="F41" s="1" t="s">
@@ -3901,7 +3889,7 @@
         <v>161</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E42" s="4"/>
       <c r="F42" s="1" t="s">
@@ -3915,7 +3903,7 @@
         <v>196</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E43" s="4"/>
       <c r="F43" s="1" t="s">
@@ -3929,7 +3917,7 @@
         <v>167</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E44" s="3"/>
       <c r="F44" s="1" t="s">
@@ -3943,7 +3931,7 @@
         <v>188</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E45" s="3"/>
       <c r="F45" s="1" t="s">
@@ -3970,7 +3958,7 @@
       </c>
       <c r="E47" s="25"/>
       <c r="F47" s="12" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -3984,7 +3972,7 @@
       </c>
       <c r="E48" s="3"/>
       <c r="F48" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -4096,17 +4084,17 @@
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="41"/>
       <c r="B57" s="44" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -4116,11 +4104,11 @@
         <v>111</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -4130,11 +4118,11 @@
         <v>135</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -4144,11 +4132,11 @@
         <v>136</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -4158,7 +4146,7 @@
         <v>141</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="1" t="s">
@@ -4172,7 +4160,7 @@
         <v>155</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="E62" s="3"/>
       <c r="F62" s="1" t="s">
@@ -4186,7 +4174,7 @@
         <v>196</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="E63" s="3"/>
       <c r="F63" s="1" t="s">
@@ -4200,7 +4188,7 @@
         <v>167</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="1" t="s">
@@ -4214,7 +4202,7 @@
         <v>188</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="1" t="s">
@@ -4432,28 +4420,28 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="41"/>
-      <c r="B82" s="53" t="s">
-        <v>380</v>
+      <c r="B82" s="54" t="s">
+        <v>376</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="41"/>
-      <c r="B83" s="53"/>
+      <c r="B83" s="54"/>
       <c r="C83" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" s="1" t="s">
@@ -4462,7 +4450,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="41"/>
-      <c r="B84" s="53"/>
+      <c r="B84" s="54"/>
       <c r="E84" s="2"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -4751,10 +4739,10 @@
       <c r="A106" s="41"/>
       <c r="B106" s="48"/>
       <c r="C106" s="1" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E106" s="3"/>
       <c r="F106" s="1" t="s">
@@ -4763,238 +4751,236 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="41"/>
-      <c r="B107" s="48"/>
-      <c r="C107" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="E107" s="3"/>
-      <c r="F107" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="B107" s="52"/>
+      <c r="C107" s="17"/>
+      <c r="D107" s="17"/>
+      <c r="E107" s="18"/>
+      <c r="F107" s="17"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="41"/>
-      <c r="B108" s="52"/>
-      <c r="C108" s="17"/>
-      <c r="D108" s="17"/>
-      <c r="E108" s="18"/>
-      <c r="F108" s="17"/>
+      <c r="B108" s="51" t="s">
+        <v>263</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="E108" s="3"/>
+      <c r="F108" s="1" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="41"/>
-      <c r="B109" s="51" t="s">
-        <v>265</v>
-      </c>
+      <c r="B109" s="48"/>
       <c r="C109" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>267</v>
       </c>
       <c r="E109" s="3"/>
       <c r="F109" s="1" t="s">
-        <v>257</v>
+        <v>149</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="41"/>
-      <c r="B110" s="48"/>
-      <c r="C110" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>268</v>
-      </c>
+      <c r="B110" s="52"/>
       <c r="E110" s="3"/>
-      <c r="F110" s="1" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="41"/>
-      <c r="B111" s="48"/>
-      <c r="C111" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="E111" s="3"/>
-      <c r="F111" s="1" t="s">
-        <v>149</v>
+      <c r="B111" s="51" t="s">
+        <v>79</v>
+      </c>
+      <c r="C111" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D111" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E111" s="19"/>
+      <c r="F111" s="15" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="41"/>
-      <c r="B112" s="52"/>
+      <c r="B112" s="48"/>
+      <c r="C112" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>148</v>
+      </c>
       <c r="E112" s="3"/>
+      <c r="F112" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="41"/>
-      <c r="B113" s="51" t="s">
-        <v>79</v>
-      </c>
-      <c r="C113" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="D113" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="E113" s="19"/>
-      <c r="F113" s="15" t="s">
-        <v>132</v>
-      </c>
+      <c r="B113" s="52"/>
+      <c r="C113" s="17"/>
+      <c r="D113" s="17"/>
+      <c r="E113" s="18"/>
+      <c r="F113" s="17"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="41"/>
-      <c r="B114" s="48"/>
-      <c r="C114" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E114" s="3"/>
-      <c r="F114" s="1" t="s">
-        <v>149</v>
+      <c r="B114" s="51" t="s">
+        <v>340</v>
+      </c>
+      <c r="C114" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>347</v>
+      </c>
+      <c r="E114" s="19"/>
+      <c r="F114" s="15" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" s="41"/>
-      <c r="B115" s="52"/>
-      <c r="C115" s="17"/>
-      <c r="D115" s="17"/>
-      <c r="E115" s="18"/>
-      <c r="F115" s="17"/>
+      <c r="B115" s="48"/>
+      <c r="C115" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="E115" s="3"/>
+      <c r="F115" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" s="41"/>
-      <c r="B116" s="51" t="s">
-        <v>344</v>
-      </c>
-      <c r="C116" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="D116" s="15" t="s">
-        <v>351</v>
-      </c>
-      <c r="E116" s="19"/>
-      <c r="F116" s="15" t="s">
-        <v>350</v>
-      </c>
+      <c r="B116" s="52"/>
+      <c r="C116" s="17"/>
+      <c r="D116" s="17"/>
+      <c r="E116" s="18"/>
+      <c r="F116" s="17"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" s="41"/>
-      <c r="B117" s="48"/>
+      <c r="B117" s="48" t="s">
+        <v>300</v>
+      </c>
       <c r="C117" s="1" t="s">
-        <v>349</v>
+        <v>330</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="E117" s="3"/>
       <c r="F117" s="1" t="s">
-        <v>149</v>
+        <v>327</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" s="41"/>
-      <c r="B118" s="52"/>
-      <c r="C118" s="17"/>
-      <c r="D118" s="17"/>
-      <c r="E118" s="18"/>
-      <c r="F118" s="17"/>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="41"/>
-      <c r="B119" s="48" t="s">
-        <v>304</v>
-      </c>
-      <c r="C119" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="E119" s="3"/>
-      <c r="F119" s="1" t="s">
+      <c r="B118" s="48"/>
+      <c r="C118" s="1" t="s">
         <v>331</v>
       </c>
+      <c r="D118" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="E118" s="3"/>
+      <c r="F118" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A119" s="42"/>
+      <c r="B119" s="49"/>
+      <c r="C119" s="27"/>
+      <c r="D119" s="27"/>
+      <c r="E119" s="28"/>
+      <c r="F119" s="27"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="41"/>
-      <c r="B120" s="48"/>
-      <c r="C120" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E120" s="3"/>
-      <c r="F120" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="42"/>
-      <c r="B121" s="49"/>
-      <c r="C121" s="27"/>
-      <c r="D121" s="27"/>
-      <c r="E121" s="28"/>
-      <c r="F121" s="27"/>
+      <c r="A120" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="B120" s="50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="41"/>
+      <c r="B121" s="48"/>
+      <c r="C121" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="B122" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C122" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D122" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="E122" s="12"/>
-      <c r="F122" s="12" t="s">
-        <v>140</v>
-      </c>
+      <c r="A122" s="41"/>
+      <c r="B122" s="52"/>
+      <c r="C122" s="17"/>
+      <c r="D122" s="17"/>
+      <c r="E122" s="17"/>
+      <c r="F122" s="17"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="41"/>
-      <c r="B123" s="48"/>
+      <c r="B123" s="51" t="s">
+        <v>183</v>
+      </c>
       <c r="C123" s="1" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="41"/>
-      <c r="B124" s="52"/>
-      <c r="C124" s="17"/>
-      <c r="D124" s="17"/>
-      <c r="E124" s="17"/>
-      <c r="F124" s="17"/>
+      <c r="B124" s="48"/>
+      <c r="C124" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="F124" s="1" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="41"/>
-      <c r="B125" s="51" t="s">
-        <v>183</v>
-      </c>
+      <c r="B125" s="48"/>
       <c r="C125" s="1" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>149</v>
@@ -5004,10 +4990,10 @@
       <c r="A126" s="41"/>
       <c r="B126" s="48"/>
       <c r="C126" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>272</v>
+        <v>178</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>149</v>
@@ -5017,10 +5003,10 @@
       <c r="A127" s="41"/>
       <c r="B127" s="48"/>
       <c r="C127" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>149</v>
@@ -5030,10 +5016,10 @@
       <c r="A128" s="41"/>
       <c r="B128" s="48"/>
       <c r="C128" s="1" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>149</v>
@@ -5041,58 +5027,58 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="41"/>
-      <c r="B129" s="48"/>
-      <c r="C129" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="F129" s="1" t="s">
-        <v>149</v>
-      </c>
+      <c r="B129" s="52"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="41"/>
-      <c r="B130" s="48"/>
-      <c r="C130" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="F130" s="1" t="s">
-        <v>149</v>
+      <c r="B130" s="51" t="s">
+        <v>206</v>
+      </c>
+      <c r="C130" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="E130" s="15"/>
+      <c r="F130" s="15" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="41"/>
-      <c r="B131" s="52"/>
+      <c r="B131" s="48"/>
+      <c r="C131" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="41"/>
-      <c r="B132" s="51" t="s">
-        <v>206</v>
-      </c>
-      <c r="C132" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="D132" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="E132" s="15"/>
-      <c r="F132" s="15" t="s">
-        <v>208</v>
+      <c r="B132" s="48"/>
+      <c r="C132" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="41"/>
       <c r="B133" s="48"/>
       <c r="C133" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>208</v>
@@ -5102,88 +5088,88 @@
       <c r="A134" s="41"/>
       <c r="B134" s="48"/>
       <c r="C134" s="1" t="s">
-        <v>215</v>
+        <v>269</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>214</v>
+        <v>270</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>219</v>
+        <v>273</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="41"/>
       <c r="B135" s="48"/>
       <c r="C135" s="1" t="s">
-        <v>205</v>
+        <v>293</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>209</v>
+        <v>294</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>208</v>
+        <v>273</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="41"/>
       <c r="B136" s="48"/>
       <c r="C136" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="F136" s="1" t="s">
         <v>273</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="F136" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="41"/>
       <c r="B137" s="48"/>
       <c r="C137" s="1" t="s">
-        <v>297</v>
+        <v>217</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>298</v>
+        <v>216</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>277</v>
+        <v>218</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="41"/>
       <c r="B138" s="48"/>
       <c r="C138" s="1" t="s">
-        <v>299</v>
+        <v>221</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>300</v>
+        <v>211</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>277</v>
+        <v>212</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="41"/>
       <c r="B139" s="48"/>
       <c r="C139" s="1" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="41"/>
       <c r="B140" s="48"/>
       <c r="C140" s="1" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>211</v>
+        <v>400</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>212</v>
@@ -5193,36 +5179,36 @@
       <c r="A141" s="41"/>
       <c r="B141" s="48"/>
       <c r="C141" s="1" t="s">
-        <v>202</v>
+        <v>352</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>220</v>
+        <v>351</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="41"/>
       <c r="B142" s="48"/>
       <c r="C142" s="1" t="s">
-        <v>235</v>
+        <v>334</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="41"/>
       <c r="B143" s="48"/>
       <c r="C143" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>355</v>
+        <v>324</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>213</v>
@@ -5230,157 +5216,114 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="41"/>
-      <c r="B144" s="48"/>
-      <c r="C144" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F144" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="B144" s="52"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="41"/>
-      <c r="B145" s="48"/>
-      <c r="C145" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="F145" s="1" t="s">
-        <v>213</v>
+      <c r="B145" s="51" t="s">
+        <v>222</v>
+      </c>
+      <c r="C145" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="E145" s="15"/>
+      <c r="F145" s="15" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="41"/>
-      <c r="B146" s="52"/>
+      <c r="B146" s="48"/>
+      <c r="C146" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>273</v>
+      </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="41"/>
-      <c r="B147" s="51" t="s">
-        <v>222</v>
-      </c>
-      <c r="C147" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>223</v>
-      </c>
-      <c r="E147" s="15"/>
-      <c r="F147" s="15" t="s">
-        <v>208</v>
+      <c r="B147" s="48"/>
+      <c r="C147" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="41"/>
       <c r="B148" s="48"/>
       <c r="C148" s="1" t="s">
-        <v>275</v>
+        <v>234</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>276</v>
+        <v>235</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>277</v>
+        <v>212</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="41"/>
       <c r="B149" s="48"/>
       <c r="C149" s="1" t="s">
-        <v>225</v>
+        <v>335</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>226</v>
+        <v>336</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="41"/>
-      <c r="B150" s="48"/>
-      <c r="C150" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>212</v>
-      </c>
+      <c r="B150" s="52"/>
+      <c r="C150" s="17"/>
+      <c r="D150" s="17"/>
+      <c r="E150" s="17"/>
+      <c r="F150" s="17"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="41"/>
-      <c r="B151" s="48"/>
+      <c r="B151" s="53" t="s">
+        <v>355</v>
+      </c>
       <c r="C151" s="1" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>213</v>
+        <v>314</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" s="41"/>
-      <c r="B152" s="52"/>
-      <c r="C152" s="17"/>
-      <c r="D152" s="17"/>
-      <c r="E152" s="17"/>
-      <c r="F152" s="17"/>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="41"/>
-      <c r="B153" s="54" t="s">
+      <c r="B152" s="53"/>
+      <c r="C152" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C153" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="41"/>
-      <c r="B154" s="54"/>
-      <c r="C154" s="1" t="s">
-        <v>361</v>
-      </c>
-      <c r="D154" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="F154" s="1" t="s">
-        <v>318</v>
+      <c r="F152" s="1" t="s">
+        <v>314</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B147:B152"/>
-    <mergeCell ref="B153:B154"/>
-    <mergeCell ref="A122:A154"/>
-    <mergeCell ref="B122:B124"/>
-    <mergeCell ref="B132:B146"/>
-    <mergeCell ref="B125:B131"/>
-    <mergeCell ref="B119:B121"/>
-    <mergeCell ref="B79:B81"/>
-    <mergeCell ref="A79:A104"/>
-    <mergeCell ref="B85:B94"/>
-    <mergeCell ref="B95:B104"/>
-    <mergeCell ref="A105:A121"/>
-    <mergeCell ref="B105:B108"/>
-    <mergeCell ref="B109:B112"/>
-    <mergeCell ref="B113:B115"/>
-    <mergeCell ref="B116:B118"/>
-    <mergeCell ref="B82:B84"/>
     <mergeCell ref="A2:A46"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B23"/>
@@ -5390,6 +5333,23 @@
     <mergeCell ref="B47:B56"/>
     <mergeCell ref="B57:B66"/>
     <mergeCell ref="B34:B46"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B79:B81"/>
+    <mergeCell ref="A79:A104"/>
+    <mergeCell ref="B85:B94"/>
+    <mergeCell ref="B95:B104"/>
+    <mergeCell ref="A105:A119"/>
+    <mergeCell ref="B105:B107"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B82:B84"/>
+    <mergeCell ref="B145:B150"/>
+    <mergeCell ref="B151:B152"/>
+    <mergeCell ref="A120:A152"/>
+    <mergeCell ref="B120:B122"/>
+    <mergeCell ref="B130:B144"/>
+    <mergeCell ref="B123:B129"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
